--- a/statistics/assesment-1/Assessment1-statistics.xlsx
+++ b/statistics/assesment-1/Assessment1-statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cadc0b9b93e25625/Desktop/TOPS/statistics/assesment-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="8_{98CC490F-8859-4BA3-9AA6-15253ECAFC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E538040-57EC-4F68-8B78-F1E4B1303096}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="8_{98CC490F-8859-4BA3-9AA6-15253ECAFC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A338E4BE-3CA0-4E17-AB41-717F735EF10A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3AD32EAF-0880-4554-8F23-BEB39B33368C}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t xml:space="preserve">MODULE - 1 INTRODUCTION TO STATISTICS </t>
   </si>
@@ -72,12 +72,6 @@
     <t>p-value</t>
   </si>
   <si>
-    <t>CONCLUSION :     P-value &gt;= 0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There is no significant difference between boys and girls with respect to intelligence </t>
-  </si>
-  <si>
     <t xml:space="preserve">Question 2. Analyze the below data and tell whether you can conclude that smoking causes 
 cancer or not? </t>
   </si>
@@ -112,10 +106,19 @@
     <t>((D24^2/E24+D25^2/E25)^2)/(((D24^2/E24)^2)/(E24-1)+((D25^2/E25)^2)/(E25-1))</t>
   </si>
   <si>
-    <t>2*(1-T.DIST.2T(C32,C33))</t>
-  </si>
-  <si>
     <t xml:space="preserve"> (row-1)*(cols-1)</t>
+  </si>
+  <si>
+    <t>(T.DIST.2T(C32,C33))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCLUSION :   </t>
+  </si>
+  <si>
+    <t>Since the p-value = 5.38916E-11 ,which is less than 0.05 ,</t>
+  </si>
+  <si>
+    <t>so there is a significant difference between boys and girls with respect to intelligence</t>
   </si>
 </sst>
 </file>
@@ -306,10 +309,6 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -609,8 +608,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA6D246-1153-4156-A6B6-6134C236AC1D}">
-  <dimension ref="B3:X40"/>
+  <dimension ref="B3:X42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
@@ -936,7 +938,7 @@
         <v>7.0175658996391963</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
@@ -948,7 +950,7 @@
         <v>167.27414848357313</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
@@ -956,16 +958,16 @@
         <v>10</v>
       </c>
       <c r="C34">
-        <f>2*(1-_xlfn.T.DIST.2T(C32,C33))</f>
-        <v>1.9999999998922169</v>
+        <f>_xlfn.T.DIST.2T(C32,C33)</f>
+        <v>5.3891590485382579E-11</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C37" s="5" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -1005,16 +1007,47 @@
       <c r="M39" s="5"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C40" t="s">
-        <v>12</v>
-      </c>
+      <c r="C40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="C42:J42"/>
     <mergeCell ref="B28:N28"/>
     <mergeCell ref="B3:M7"/>
     <mergeCell ref="B9:M18"/>
     <mergeCell ref="C37:M39"/>
+    <mergeCell ref="C40:J41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1033,7 +1066,7 @@
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -1086,16 +1119,16 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
@@ -1106,7 +1139,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4">
         <v>220</v>
@@ -1120,7 +1153,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4">
         <v>350</v>
@@ -1134,7 +1167,7 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" s="4">
         <v>680</v>
@@ -1160,13 +1193,13 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
@@ -1176,7 +1209,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C22" s="4">
         <f>(E12*$C$14)/$E$14</f>
@@ -1189,7 +1222,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4">
         <f>(E13*$C$14)/$E$14</f>
@@ -1207,18 +1240,18 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C28" s="2">
         <f>((C12-C22)^2)/C22</f>
@@ -1231,7 +1264,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C29" s="2">
         <f>((C13-C23)^2)/C23</f>
@@ -1244,7 +1277,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C31">
         <f>SUM(C28:C29)+SUM(D28:D29)</f>
@@ -1260,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.3">
@@ -1274,7 +1307,7 @@
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
